--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liamdeng/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liamdeng/Desktop/T1Nexus-Catalog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DD9618-7D39-F348-B050-D7DB5F99F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3E2B2A-65CE-074C-9EF2-6946406C77EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16640" firstSheet="3" activeTab="6" xr2:uid="{A393CFD8-9608-44C3-AD50-F6EC253B6E67}"/>
   </bookViews>
@@ -42494,7 +42494,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:24">
       <c r="A81" s="1" t="s">
         <v>350</v>
       </c>
@@ -42552,7 +42552,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:24">
       <c r="A82" s="1" t="s">
         <v>1720</v>
       </c>
@@ -42610,7 +42610,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:24">
       <c r="A83" s="1" t="s">
         <v>1725</v>
       </c>
@@ -42668,7 +42668,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:24">
       <c r="A84" s="1" t="s">
         <v>1730</v>
       </c>
@@ -42726,7 +42726,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:24">
       <c r="B85" s="139"/>
       <c r="C85" s="139"/>
       <c r="J85" t="s">
@@ -42734,16 +42734,18 @@
       </c>
       <c r="T85" s="139"/>
     </row>
-    <row r="86" spans="1:22">
-      <c r="B86" s="120" t="s">
+    <row r="86" spans="1:24">
+      <c r="B86" s="120"/>
+      <c r="C86" s="120"/>
+      <c r="T86" s="139"/>
+      <c r="W86" s="120" t="s">
         <v>992</v>
       </c>
-      <c r="C86" s="120" t="s">
+      <c r="X86" s="120" t="s">
         <v>1735</v>
       </c>
-      <c r="T86" s="139"/>
-    </row>
-    <row r="87" spans="1:22">
+    </row>
+    <row r="87" spans="1:24">
       <c r="B87" s="120" t="s">
         <v>1736</v>
       </c>
@@ -42789,7 +42791,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="88" spans="1:22" ht="16">
+    <row r="88" spans="1:24" ht="16">
       <c r="B88" s="122" t="s">
         <v>1739</v>
       </c>
@@ -42832,7 +42834,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="89" spans="1:22" ht="16">
+    <row r="89" spans="1:24" ht="16">
       <c r="B89" s="122" t="s">
         <v>1743</v>
       </c>
@@ -42889,7 +42891,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="90" spans="1:22" ht="16">
+    <row r="90" spans="1:24" ht="16">
       <c r="B90" s="122" t="s">
         <v>636</v>
       </c>
@@ -42944,7 +42946,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="91" spans="1:22" ht="16">
+    <row r="91" spans="1:24" ht="16">
       <c r="B91" s="122" t="s">
         <v>1753</v>
       </c>
@@ -42987,7 +42989,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="92" spans="1:22" ht="16">
+    <row r="92" spans="1:24" ht="16">
       <c r="B92" s="122" t="s">
         <v>1755</v>
       </c>
@@ -43038,7 +43040,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="93" spans="1:22" ht="16">
+    <row r="93" spans="1:24" ht="16">
       <c r="B93" s="122" t="s">
         <v>1758</v>
       </c>
@@ -43087,7 +43089,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="94" spans="1:22" ht="16">
+    <row r="94" spans="1:24" ht="16">
       <c r="B94" s="122" t="s">
         <v>1762</v>
       </c>
@@ -43135,7 +43137,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="95" spans="1:22" ht="16">
+    <row r="95" spans="1:24" ht="16">
       <c r="B95" s="122" t="s">
         <v>770</v>
       </c>
@@ -43189,7 +43191,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="96" spans="1:22" ht="16">
+    <row r="96" spans="1:24" ht="16">
       <c r="B96" s="122" t="s">
         <v>1765</v>
       </c>
@@ -52812,21 +52814,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D11E57DF58B07A4DB471822BF43B5FA7" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6bc0c658be4d2e15c64799289e01d2e2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00b19f84-1261-4752-a2be-1aa9b88346f0" xmlns:ns3="55ed4eee-dc54-4d4e-b73c-f209ead08a95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d4d3079a6cc0935fc4ed07787cba1b" ns2:_="" ns3:_="">
     <xsd:import namespace="00b19f84-1261-4752-a2be-1aa9b88346f0"/>
@@ -53003,24 +52990,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C33E1A5-9541-45AE-99B5-4394F827DF05}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -53037,4 +53022,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liamdeng/Desktop/T1Nexus-Catalog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3E2B2A-65CE-074C-9EF2-6946406C77EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C531B778-4411-024B-AB2A-EF3998823F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16640" firstSheet="3" activeTab="6" xr2:uid="{A393CFD8-9608-44C3-AD50-F6EC253B6E67}"/>
   </bookViews>
@@ -147,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10046" uniqueCount="3238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10049" uniqueCount="3240">
   <si>
     <t>Group</t>
   </si>
@@ -10039,6 +10039,12 @@
   </si>
   <si>
     <t>T1Neuxs Keystone Coupler UTP Cat6 RJ45</t>
+  </si>
+  <si>
+    <t>T1-Testing-Testing-Te</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -42727,8 +42733,16 @@
       </c>
     </row>
     <row r="85" spans="1:24">
-      <c r="B85" s="139"/>
+      <c r="B85" s="139" t="s">
+        <v>3238</v>
+      </c>
       <c r="C85" s="139"/>
+      <c r="D85" t="s">
+        <v>397</v>
+      </c>
+      <c r="E85" t="s">
+        <v>3239</v>
+      </c>
       <c r="J85" t="s">
         <v>1734</v>
       </c>
@@ -52814,6 +52828,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D11E57DF58B07A4DB471822BF43B5FA7" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6bc0c658be4d2e15c64799289e01d2e2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00b19f84-1261-4752-a2be-1aa9b88346f0" xmlns:ns3="55ed4eee-dc54-4d4e-b73c-f209ead08a95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d4d3079a6cc0935fc4ed07787cba1b" ns2:_="" ns3:_="">
     <xsd:import namespace="00b19f84-1261-4752-a2be-1aa9b88346f0"/>
@@ -52990,22 +53019,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C33E1A5-9541-45AE-99B5-4394F827DF05}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -53022,21 +53053,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liamdeng/Desktop/T1Nexus-Catalog/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C531B778-4411-024B-AB2A-EF3998823F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B6B847-8BF8-A144-8B87-4D16BA0D529F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="29400" windowHeight="16640" firstSheet="3" activeTab="6" xr2:uid="{A393CFD8-9608-44C3-AD50-F6EC253B6E67}"/>
   </bookViews>
@@ -147,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10049" uniqueCount="3240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10046" uniqueCount="3238">
   <si>
     <t>Group</t>
   </si>
@@ -10039,12 +10039,6 @@
   </si>
   <si>
     <t>T1Neuxs Keystone Coupler UTP Cat6 RJ45</t>
-  </si>
-  <si>
-    <t>T1-Testing-Testing-Te</t>
-  </si>
-  <si>
-    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -42733,16 +42727,8 @@
       </c>
     </row>
     <row r="85" spans="1:24">
-      <c r="B85" s="139" t="s">
-        <v>3238</v>
-      </c>
+      <c r="B85" s="139"/>
       <c r="C85" s="139"/>
-      <c r="D85" t="s">
-        <v>397</v>
-      </c>
-      <c r="E85" t="s">
-        <v>3239</v>
-      </c>
       <c r="J85" t="s">
         <v>1734</v>
       </c>
@@ -52828,21 +52814,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D11E57DF58B07A4DB471822BF43B5FA7" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6bc0c658be4d2e15c64799289e01d2e2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="00b19f84-1261-4752-a2be-1aa9b88346f0" xmlns:ns3="55ed4eee-dc54-4d4e-b73c-f209ead08a95" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1d4d3079a6cc0935fc4ed07787cba1b" ns2:_="" ns3:_="">
     <xsd:import namespace="00b19f84-1261-4752-a2be-1aa9b88346f0"/>
@@ -53019,24 +52990,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C33E1A5-9541-45AE-99B5-4394F827DF05}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -53053,4 +53022,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB5C838B-6C76-4B70-B9E0-A1CA2AF139EB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA60FA70-E6AC-446F-88E4-09175203B2DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>